--- a/system_development/v0.1.0/BOM-v0.1.0.xlsx
+++ b/system_development/v0.1.0/BOM-v0.1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Fieldable-NV-Center\system_development\v0.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05B22EB-D491-4C8E-BDCD-B5EEEBD292FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BA0BE6-0996-4FFD-A726-D831776CF1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
